--- a/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3397,7 +3397,7 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31.996339" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="28.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3457,21 +3457,22 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="5" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16.853482" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.139196" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.567768" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14.282054" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13.424911" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12.567768" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.139196" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17.424911" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.710625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.282054" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.853482" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.424911" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.282054" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="9.139196" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="7.853482" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="7.996339" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="6.424911" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="5.139196" style="0" customWidth="1"/>
   </x:cols>
@@ -3553,23 +3554,23 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="51.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="85.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="86.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="85.424911" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="83.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="81.282054" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="78.424911" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="74.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="70.567768" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="65.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="60.710625" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="55.139196" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="49.282054" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="42.853482" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="35.996339" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="29.139196" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="86.139196" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="86.853482" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="85.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="84.139196" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="81.567768" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="78.710625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="75.139196" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="70.853482" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="66.139196" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="60.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="55.424911" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="49.424911" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="42.996339" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="36.139196" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="29.282054" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="21.853482" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="14.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3669,7 +3670,7 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="34.5" customHeight="1">
+    <x:row r="5" spans="1:1" ht="35.25" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>10</x:v>
       </x:c>
@@ -3684,62 +3685,62 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="52.5" customHeight="1">
+    <x:row r="8" spans="1:1" ht="53.25" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="57.75" customHeight="1">
+    <x:row r="9" spans="1:1" ht="58.5" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="62.25" customHeight="1">
+    <x:row r="10" spans="1:1" ht="63" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="66.75" customHeight="1">
+    <x:row r="11" spans="1:1" ht="67.5" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="70.5" customHeight="1">
+    <x:row r="12" spans="1:1" ht="71.25" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="73.5" customHeight="1">
+    <x:row r="13" spans="1:1" ht="75" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="76.5" customHeight="1">
+    <x:row r="14" spans="1:1" ht="77.25" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="78.75" customHeight="1">
+    <x:row r="15" spans="1:1" ht="79.5" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="80.25" customHeight="1">
+    <x:row r="16" spans="1:1" ht="81" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="81" customHeight="1">
+    <x:row r="17" spans="1:1" ht="81.75" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="81" customHeight="1">
+    <x:row r="18" spans="1:1" ht="82.5" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="81" customHeight="1">
+    <x:row r="19" spans="1:1" ht="81.75" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -3771,87 +3772,87 @@
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="47.25" customHeight="1">
+    <x:row r="3" spans="1:1" ht="46.5" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="75.75" customHeight="1">
+    <x:row r="4" spans="1:1" ht="75" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="102.75" customHeight="1">
+    <x:row r="5" spans="1:1" ht="102" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="129.75" customHeight="1">
+    <x:row r="6" spans="1:1" ht="128.25" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="155.25" customHeight="1">
+    <x:row r="7" spans="1:1" ht="153" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="180" customHeight="1">
+    <x:row r="8" spans="1:1" ht="177" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="203.25" customHeight="1">
+    <x:row r="9" spans="1:1" ht="200.25" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="225" customHeight="1">
+    <x:row r="10" spans="1:1" ht="221.25" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="244.5" customHeight="1">
+    <x:row r="11" spans="1:1" ht="240.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="263.25" customHeight="1">
+    <x:row r="12" spans="1:1" ht="258.75" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="279" customHeight="1">
+    <x:row r="13" spans="1:1" ht="274.5" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="293.25" customHeight="1">
+    <x:row r="14" spans="1:1" ht="288" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="304.5" customHeight="1">
+    <x:row r="15" spans="1:1" ht="300" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="314.25" customHeight="1">
+    <x:row r="16" spans="1:1" ht="309" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="321" customHeight="1">
+    <x:row r="17" spans="1:1" ht="315.75" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="325.5" customHeight="1">
+    <x:row r="18" spans="1:1" ht="320.25" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="327.75" customHeight="1">
+    <x:row r="19" spans="1:1" ht="322.5" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>

--- a/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3554,24 +3554,24 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="51.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="86.139196" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="86.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="85.710625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="84.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="81.567768" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="78.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="75.139196" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="70.853482" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="66.139196" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="60.996339" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="55.424911" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="49.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="42.996339" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="36.139196" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="29.282054" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="21.853482" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14.567768" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="53.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="88.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="88.853482" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="87.567768" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="85.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="83.567768" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="80.424911" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="76.567768" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="72.282054" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="67.424911" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="62.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="50.282054" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="43.853482" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="36.710625" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="29.710625" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="22.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3772,87 +3772,87 @@
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:1" ht="46.5" customHeight="1">
+    <x:row r="3" spans="1:1" ht="47.25" customHeight="1">
       <x:c r="A3" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:1" ht="75" customHeight="1">
+    <x:row r="4" spans="1:1" ht="75.75" customHeight="1">
       <x:c r="A4" s="5" t="s">
         <x:v>45</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1" ht="102" customHeight="1">
+    <x:row r="5" spans="1:1" ht="103.5" customHeight="1">
       <x:c r="A5" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:1" ht="128.25" customHeight="1">
+    <x:row r="6" spans="1:1" ht="130.5" customHeight="1">
       <x:c r="A6" s="7" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:1" ht="153" customHeight="1">
+    <x:row r="7" spans="1:1" ht="156" customHeight="1">
       <x:c r="A7" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:1" ht="177" customHeight="1">
+    <x:row r="8" spans="1:1" ht="180.75" customHeight="1">
       <x:c r="A8" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:1" ht="200.25" customHeight="1">
+    <x:row r="9" spans="1:1" ht="204" customHeight="1">
       <x:c r="A9" s="10" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:1" ht="221.25" customHeight="1">
+    <x:row r="10" spans="1:1" ht="225.75" customHeight="1">
       <x:c r="A10" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:1" ht="240.75" customHeight="1">
+    <x:row r="11" spans="1:1" ht="246" customHeight="1">
       <x:c r="A11" s="12" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1" ht="258.75" customHeight="1">
+    <x:row r="12" spans="1:1" ht="264" customHeight="1">
       <x:c r="A12" s="13" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:1" ht="274.5" customHeight="1">
+    <x:row r="13" spans="1:1" ht="280.5" customHeight="1">
       <x:c r="A13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:1" ht="288" customHeight="1">
+    <x:row r="14" spans="1:1" ht="294.75" customHeight="1">
       <x:c r="A14" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:1" ht="300" customHeight="1">
+    <x:row r="15" spans="1:1" ht="306" customHeight="1">
       <x:c r="A15" s="16" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:1" ht="309" customHeight="1">
+    <x:row r="16" spans="1:1" ht="315.75" customHeight="1">
       <x:c r="A16" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:1" ht="315.75" customHeight="1">
+    <x:row r="17" spans="1:1" ht="322.5" customHeight="1">
       <x:c r="A17" s="18" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:1" ht="320.25" customHeight="1">
+    <x:row r="18" spans="1:1" ht="327.75" customHeight="1">
       <x:c r="A18" s="19" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:1" ht="322.5" customHeight="1">
+    <x:row r="19" spans="1:1" ht="329.25" customHeight="1">
       <x:c r="A19" s="20" t="s">
         <x:v>60</x:v>
       </x:c>
